--- a/aq_files/0734.xlsx
+++ b/aq_files/0734.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tuple" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tuple is:</t>
+          <t>Which is mutable?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) immutable B) mutable C) none D) both</t>
+          <t>A) list B) tuple C) string D) int</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tuple uses:</t>
+          <t>Which is unordered?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) () B) [] C) {} D) &lt;&gt;</t>
+          <t>A) set B) list C) tuple D) string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuple allows duplicates?</t>
+          <t>Dictionary stores:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A) Yes B) No C) None D) maybe</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) key-value B) values only C) keys only D) none</t>
         </is>
       </c>
     </row>
@@ -512,39 +507,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tuple is faster than list?</t>
+          <t>Which is immutable?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A) Yes B) No C) Same D) None</t>
+          <t>A) tuple B) list C) set D) dict</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Convert list to tuple.</t>
+          <t>Which DS allows duplicates?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>A) list B) set C) dict D) none</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -556,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find max in tuple.</t>
+          <t>Find duplicate elements in an array.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -578,7 +573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Count elements in tuple.</t>
+          <t>Find intersection of two arrays.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -600,17 +595,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find index of element.</t>
+          <t>Check if list is palindrome.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -622,17 +612,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unpack tuple values.</t>
+          <t>Remove duplicates from list.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -644,7 +629,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swap values using tuple.</t>
+          <t>Find frequency of elements.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +639,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -666,7 +651,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Find common elements in tuples.</t>
+          <t>Find max and min in list.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +661,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -688,17 +673,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Check tuple palindrome.</t>
+          <t>Merge two lists.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -710,7 +690,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Merge two tuples.</t>
+          <t>Find second largest element.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +700,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -732,7 +712,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sort tuple elements.</t>
+          <t>Sort list without built-in.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +722,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -754,7 +734,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Convert tuple to list and modify.</t>
+          <t>Find common elements.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +744,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -776,17 +756,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find frequency in tuple.</t>
+          <t>Reverse list.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -798,7 +773,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find sum of tuple elements.</t>
+          <t>Find sum of elements.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -820,17 +795,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nested tuple traversal.</t>
+          <t>Check if element exists.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -842,17 +812,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find largest tuple element.</t>
+          <t>Count occurrences.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -864,7 +829,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Check tuple equality.</t>
+          <t>Find unique elements.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +839,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
